--- a/src/BARB/ex02_BARB_glossary.xlsx
+++ b/src/BARB/ex02_BARB_glossary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,224 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Понятие</t>
+  </si>
+  <si>
+    <t>Определение</t>
+  </si>
+  <si>
+    <t>Программное обеспечение, предназначенное для автоматизации процесса бронирования услуг клиентами через интернет. Является центральным элементом данного проекта.</t>
+  </si>
+  <si>
+    <t>1. Система онлайн-записи</t>
+  </si>
+  <si>
+    <t>2. Клиентская база </t>
+  </si>
+  <si>
+    <t>Совокупность данных о всех клиентах барбершопа (контактная информация, история посещений, предпочтения). Цель проекта — ее расширение.</t>
+  </si>
+  <si>
+    <t>Количество времени и усилий, затрачиваемых сотрудниками (в первую очередь менеджерами) на рутинные операции. Проект нацелен на их снижение.</t>
+  </si>
+  <si>
+    <t>3. Трудозатраты</t>
+  </si>
+  <si>
+    <t>4. Ручной труд </t>
+  </si>
+  <si>
+    <t>Операции, выполняемые сотрудниками вручную (например, прием звонков для записи, запись в бумажный журнал). Подлежит автоматизации.</t>
+  </si>
+  <si>
+    <t>5. Автоматическое информирование</t>
+  </si>
+  <si>
+    <t>Функция системы, позволяющая без участия человека отправлять клиентам уведомления и напоминания по заданному сценарию.</t>
+  </si>
+  <si>
+    <t>6. Зарегистрированный пользователь</t>
+  </si>
+  <si>
+    <t>Клиент, создавший личный кабинет в системе (обычно с помощью email или номера телефона). Может иметь расширенные возможности (просмотр истории записей, быстрая запись).</t>
+  </si>
+  <si>
+    <t>7. Незарегистрированный посетитель</t>
+  </si>
+  <si>
+    <t>Пользователь, который может совершить разовую запись без создания учетной записи в системе.</t>
+  </si>
+  <si>
+    <t>8. Тип услуги</t>
+  </si>
+  <si>
+    <t>Высокоуровневая категоризация услуг барбершопа. В тексте указаны два основных типа: парикмахерские и косметологические.</t>
+  </si>
+  <si>
+    <t>9. Номенклатура услуг</t>
+  </si>
+  <si>
+    <t>Конкретный перечень услуг, предоставляемых барбершопом (например, "Стрижка машинкой", "Королевское бритье", "Уход за бородой").</t>
+  </si>
+  <si>
+    <t>10. Мастер</t>
+  </si>
+  <si>
+    <t>Специалист (барбер, косметолог), непосредственно оказывающий услуги клиенту. В системе за ним закрепляются оказываемые услуги и расписание.</t>
+  </si>
+  <si>
+    <t>11. Свободные интервалы</t>
+  </si>
+  <si>
+    <t>Доступные для бронирования слоты времени в расписании мастеров, которые система отображает клиенту при записи.</t>
+  </si>
+  <si>
+    <t>12. Канал связи</t>
+  </si>
+  <si>
+    <t>Способ отправки уведомлений клиенту. Система должна поддерживать интеграцию с несколькими каналами: Telegram, WhatsApp, VK, СМС.</t>
+  </si>
+  <si>
+    <t>13. Расписание отправки уведомлений</t>
+  </si>
+  <si>
+    <t>Настраиваемый менеджером набор правил, определяющий, когда и какие напоминания (за день, за час) отправляются клиенту.</t>
+  </si>
+  <si>
+    <t>14. Опрос клиента</t>
+  </si>
+  <si>
+    <t>Функция системы, которая после оказания услуги запрашивает у клиента оценку и предложения по улучшению работы (фидбек).</t>
+  </si>
+  <si>
+    <t>15. Менеджер</t>
+  </si>
+  <si>
+    <t>Административный сотрудник, отвечающий за конфигурацию и работу системы: управление расписанием, услугами, мастерами, а также за ручное взаимодействие с клиентами и финансовые операции.</t>
+  </si>
+  <si>
+    <t>16. Расписание мастера</t>
+  </si>
+  <si>
+    <t>График работы каждого мастера, включающий рабочие часы, перерывы, отпуска и уже занятые клиентами интервалы. Вводится и корректируется менеджером.</t>
+  </si>
+  <si>
+    <t>17. Отметка о выполнении услуги</t>
+  </si>
+  <si>
+    <t>Действие менеджера или мастера в системе, подтверждающее, что услуга была оказана. Этот статус может запускать отправку опроса и закрытие финансовой операции.</t>
+  </si>
+  <si>
+    <t>18. Прием оплаты</t>
+  </si>
+  <si>
+    <t>Процесс внесения данных о получении денежных средств от клиента в систему с возможностью последующей передачи этой информации в бухгалтерию.</t>
+  </si>
+  <si>
+    <t>19. Отчет о выполненных услугах</t>
+  </si>
+  <si>
+    <t>Аналитический документ, формируемый системой на основе данных о завершенных записях. Необходим для анализа выручки, загрузки мастеров и популярности услуг.</t>
+  </si>
+  <si>
+    <t>20. Личный кабинет мастера</t>
+  </si>
+  <si>
+    <t>Раздел системы, доступный мастеру, где он может просматривать свое расписание, предстоящие записи и отзывы клиентов на свои услуги</t>
+  </si>
+  <si>
+    <t>01.1</t>
+  </si>
+  <si>
+    <t>01.2</t>
+  </si>
+  <si>
+    <t>01.3</t>
+  </si>
+  <si>
+    <t>01.4</t>
+  </si>
+  <si>
+    <t>01.5</t>
+  </si>
+  <si>
+    <t>01.6</t>
+  </si>
+  <si>
+    <t>01.7</t>
+  </si>
+  <si>
+    <t>01.8</t>
+  </si>
+  <si>
+    <t>01.9</t>
+  </si>
+  <si>
+    <t>01.10</t>
+  </si>
+  <si>
+    <t>01.11</t>
+  </si>
+  <si>
+    <t>01.12</t>
+  </si>
+  <si>
+    <t>01.13</t>
+  </si>
+  <si>
+    <t>01.14</t>
+  </si>
+  <si>
+    <t>01.15</t>
+  </si>
+  <si>
+    <t>01.16</t>
+  </si>
+  <si>
+    <t>01.17</t>
+  </si>
+  <si>
+    <t>01.18</t>
+  </si>
+  <si>
+    <t>01.19</t>
+  </si>
+  <si>
+    <t>01.20</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -49,11 +259,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -69,9 +287,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -109,12 +327,12 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -149,7 +367,7 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -181,7 +399,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -331,9 +549,266 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="38.21875" customWidth="1"/>
+    <col min="3" max="3" width="80.21875" customWidth="1"/>
+    <col min="5" max="5" width="39" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>